--- a/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
@@ -159,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Denmark installed capacity, start of month: wind, solar, thermal (Energinet / Danish Energy Agency) (to Sep/26)</a:t>
+              <a:t>Denmark installed capacity, start of month (Energinet) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -351,7 +351,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Denmark net capacity additions per month: solar and wind (Energinet) (to Sep/26)</a:t>
+              <a:t>Denmark net capacity additions per month (Energinet) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -6156,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6435,157 +6435,133 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45292</v>
+        <v>45658</v>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7506.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5638</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1868.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4150</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3228</v>
+      </c>
+      <c r="E14" t="n">
+        <v>922</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Thermal_unsplit_MW (ENTSO-E: total less wind less solar)</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>6730.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6730.9</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>6121.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6150</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Wind_MW</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>7506.8</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5638</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1868.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C16" t="n">
+        <v>7526.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5639</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1887.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Solar_MW</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>4150</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3228</v>
-      </c>
-      <c r="E15" t="n">
-        <v>922</v>
-      </c>
-      <c r="F15" t="n">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="C17" t="n">
+        <v>5067.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3120</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1947.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Thermal_unsplit_MW (ENTSO-E: total less wind less solar)</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>6121.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6150</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Wind_MW</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>7526.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5639</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1887.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Solar_MW</t>
-        </is>
-      </c>
       <c r="C18" t="n">
-        <v>5067.5</v>
+        <v>5454.2</v>
       </c>
       <c r="D18" t="n">
-        <v>3120</v>
+        <v>6114</v>
       </c>
       <c r="E18" t="n">
-        <v>1947.5</v>
+        <v>-659.8</v>
       </c>
       <c r="F18" t="n">
-        <v>62.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Thermal_unsplit_MW (ENTSO-E: total less wind less solar)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5454.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6114</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-659.8</v>
-      </c>
-      <c r="F19" t="n">
         <v>-10.8</v>
       </c>
     </row>
@@ -6633,17 +6609,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:05</t>
+          <t>2026-10-12 04:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12771 rows from 2016-01-01; latest month 2026-09-01</t>
+          <t>495 rows from 2026-05-01; latest month 2026-09-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28eac98a0adf6342</t>
+          <t>1311c4eeec1715d8</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:07</t>
+          <t>2026-10-12 04:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/denmark_power_capacity_monthly.xlsx
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:09</t>
+          <t>2026-10-28 01:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
